--- a/financial/model/freight-recovery-financial-model.xlsx
+++ b/financial/model/freight-recovery-financial-model.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Public cloud median ~4.1x EV/NTM (Jan 2026)</t>
+          <t>Public cloud median ~4.1x EV/NTM (Jan 2026); latest overall median 4.5x (16 Oct 2026)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://cloudedjudgement.substack.com/</t>
+          <t>https://cloudedjudgement.substack.com/p/clouded-judgement-101626-the-diffusion</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dated; not re-verified for this workbook</t>
+          <t>VERIFIED primary (latest); the workbook value is the older January figure</t>
         </is>
       </c>
     </row>
